--- a/xlsx/EIGO_NO_PARTNERに出てくる文.xlsx
+++ b/xlsx/EIGO_NO_PARTNERに出てくる文.xlsx
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>あなたは数学の先生ですか。 いいえ、違います。</t>
+          <t>あなたは数学の先生ですか。いいえ、違います。</t>
         </is>
       </c>
     </row>
